--- a/deliverables/青岛红枫路交通事故_肇事方沟通流程表_20260817.xlsx
+++ b/deliverables/青岛红枫路交通事故_肇事方沟通流程表_20260817.xlsx
@@ -24,7 +24,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'12步沟通顺序'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'对方一句话怎么接'!$A$1:$B$12</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'对方一句话怎么接'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'可以说与不可以说'!$A$1:$C$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'可以说与不可以说'!$A$1:$C$36</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'可以说与不可以说'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'律师决策'!$A$1:$C$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'律师决策'!$1:$2</definedName>
@@ -1522,7 +1522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2047,8 +2047,93 @@
         </is>
       </c>
     </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>绝对不说</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>不要对美团说「我们老板刘孝春会把小姑娘赔不起的都补上」——等于放她走。</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>备忘录禁用清单</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>绝对不说</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>不要把刘孝春写成工伤单位去人社局；退休未签合同，工伤这条很窄。</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>备忘录禁用清单</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>绝对不说</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>不要对外说叉车。涉事是货运三轮。</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>备忘录禁用清单</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>绝对不说</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>不要把律师举例里的九级、25–30 万当成本案结论。</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>备忘录禁用清单</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>绝对不说</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>不要把「骑手 70%、用工方 30%」说成交警认定——那是内部讨论。</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>备忘录禁用清单</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C31"/>
+  <autoFilter ref="A1:C36"/>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>

--- a/deliverables/青岛红枫路交通事故_肇事方沟通流程表_20260817.xlsx
+++ b/deliverables/青岛红枫路交通事故_肇事方沟通流程表_20260817.xlsx
@@ -24,7 +24,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'12步沟通顺序'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'对方一句话怎么接'!$A$1:$B$12</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'对方一句话怎么接'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'可以说与不可以说'!$A$1:$C$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'可以说与不可以说'!$A$1:$C$39</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'可以说与不可以说'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'律师决策'!$A$1:$C$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'律师决策'!$1:$2</definedName>
@@ -1522,7 +1522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>请平台和保险进群。个人经济情况理解，但规则归规则。</t>
+          <t>请平台和保险进群。8 月 17 日你说已打客服、加 1866 微信，现在要书面结果：人民医院认不认、赔付比例。</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>不要把「骑手 70%、用工方 30%」说成交警认定——那是内部讨论。</t>
+          <t>不要把「骑手 70%、用工方 30%、驾驶人 0 责」说成交警认定——那是内部讨论。</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -2132,8 +2132,59 @@
         </is>
       </c>
     </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>绝对不说</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>不要把记录 16 远洋工伤九级、25–30 万当成本案。</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>备忘录禁用清单</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>绝对不说</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>不要把记录 13 里蒋玉年、26 床、8000 元写进本案费用。</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>备忘录禁用清单</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="36" customHeight="1">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>绝对不说</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>不要写成给孙总干活。</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>备忘录禁用清单</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C36"/>
+  <autoFilter ref="A1:C39"/>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>

--- a/deliverables/青岛红枫路交通事故_肇事方沟通流程表_20260817.xlsx
+++ b/deliverables/青岛红枫路交通事故_肇事方沟通流程表_20260817.xlsx
@@ -24,7 +24,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'12步沟通顺序'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'对方一句话怎么接'!$A$1:$B$12</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'对方一句话怎么接'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'可以说与不可以说'!$A$1:$C$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'可以说与不可以说'!$A$1:$C$42</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'可以说与不可以说'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'律师决策'!$A$1:$C$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'律师决策'!$1:$2</definedName>
@@ -1522,7 +1522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>请平台和保险进群。8 月 17 日你说已打客服、加 1866 微信，现在要书面结果：人民医院认不认、赔付比例。</t>
+          <t>请拉群确认保险公司名称、保单号、限额和书面赔付比例。人民医院可以赔，比例还没书面。</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>不要为了走一般程序去赌全责，那会把无牌/无证风险砸在己方。</t>
+          <t>不要为了走一般程序去赌全责。驾驶人有证，但无牌风险仍在，程序由律师定。</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>不要无发票的现金开支事后补口。</t>
+          <t>不要把 3 万垫付说成借款或事故已经了结。</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>不要对保险公司说「朋友说公立二甲一定能报」。</t>
+          <t>不要去人社局报工伤。未签劳动合同，不具备工伤认定条件。</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>不要把医保结算说成美团险已经确认。</t>
+          <t>不要等法院先确认雇佣关系才去写收据、要欠薪——现在就能写。</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>不要说伤者已经进入康复期。</t>
+          <t>不要无发票的现金开支事后补口。</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>不要装病、不要出院再入院绕考核、不要代扮交警。</t>
+          <t>不要对保险公司说「朋友说公立二甲一定能报」。</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>不要对美团说「我们老板刘孝春会把小姑娘赔不起的都补上」——等于放她走。</t>
+          <t>不要把医保结算说成美团险已经确认。</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>不要把刘孝春写成工伤单位去人社局；退休未签合同，工伤这条很窄。</t>
+          <t>不要说伤者已经进入康复期。</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>不要对外说叉车。涉事是货运三轮。</t>
+          <t>不要装病、不要出院再入院绕考核、不要代扮交警。</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>不要把律师举例里的九级、25–30 万当成本案结论。</t>
+          <t>不要对美团说「我们老板刘孝春会把小姑娘赔不起的都补上」——等于放她走。</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>不要把「骑手 70%、用工方 30%、驾驶人 0 责」说成交警认定——那是内部讨论。</t>
+          <t>不要把刘孝春写成工伤单位去人社局；未签劳动合同，工伤已排除。</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>不要把记录 16 远洋工伤九级、25–30 万当成本案。</t>
+          <t>不要对外说叉车。涉事是货运三轮。</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>不要把记录 13 里蒋玉年、26 床、8000 元写进本案费用。</t>
+          <t>不要把律师举例里的九级、25–30 万当成本案结论。</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -2174,17 +2174,68 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
+          <t>不要把「骑手 70%、用工方 30%、驾驶人 0 责」说成交警认定——那是内部讨论。</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>备忘录禁用清单</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="36" customHeight="1">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>绝对不说</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>不要把记录 16 远洋工伤九级、25–30 万当成本案。</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>备忘录禁用清单</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="36" customHeight="1">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>绝对不说</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>不要把记录 13 里蒋玉年、26 床、8000 元写进本案费用。</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>备忘录禁用清单</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="36" customHeight="1">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>绝对不说</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
           <t>不要写成给孙总干活。</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>备忘录禁用清单</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C39"/>
+  <autoFilter ref="A1:C42"/>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>

--- a/deliverables/青岛红枫路交通事故_肇事方沟通流程表_20260817.xlsx
+++ b/deliverables/青岛红枫路交通事故_肇事方沟通流程表_20260817.xlsx
@@ -603,7 +603,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>第一场跟肇事者谈，目的不是签总包、不是定残、不是逼她承认全责。 必须拿到：美团站点/平台和保险公司进同一个微信群；保险是否认市北区人民医院（抚顺路院区）；已发生医疗费谁先垫、何时转到医院账户；后续材料怎么交。 态度：冷静、有检查号、有发票意识。她个人没钱，不跟她吵架要现金，要她把保险和站点叫来。 交警视频已经排除全责。对外说「双方都有责任，你们后方未保持车距，我们按认定书走」，不要说对方全责。</t>
+          <t>第一场跟肇事者谈，目的不是谈总赔偿数额、不是签总包、不是定残、不是逼她承认全责。 必须拿到：美团站点/平台和保险公司进同一个微信群；保险是否认市北区人民医院（抚顺路院区）；已发生医疗费谁先垫、何时转到医院账户；后续材料怎么交。 态度：冷静、有检查号、有发票意识。她个人没钱，不跟她吵架要现金，要她把保险和站点叫来。 交警视频已经排除全责。对外说「双方都有责任，你们后方未保持车距，我们按认定书走」，不要说对方全责。</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>不谈残级，不签一次性了结，除非律师看过保险条款。</t>
+          <t>今天不谈总赔偿数额、不谈残级，不签一次性了结。费用还在发生，等认定书和治疗稳定后再按票算。</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>一次性打包，以后不再找你们</t>
+          <t>现在一共要多少钱 / 一次性打包了结</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>不要对外说「已经几级伤残」。</t>
+          <t>不要现在谈一个总赔偿数额、不要对外说「已经几级伤残」。</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
